--- a/assets/files/eac-parts-request-template.xlsx
+++ b/assets/files/eac-parts-request-template.xlsx
@@ -3165,7 +3165,7 @@
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation sqref="D5:D204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Any,ATE,BERU,BOGE,Blue Print,BorgWarner,Bosch,Brembo,Dayco,Delphi,FAG,FILTRON,HEPU,INA,LEMFÖRDER,LuK,MAHLE,MANN-FILTER,PURFLUX,ProVia,SACHS,SWAG,TEXTAR,TRW,VDO,Valeo,Vitesco Technologies,WABCO,ZF Parts,febi"</formula1>
+      <formula1>"Any,ATE,BERU,BOGE,Blue Print,BorgWarner,Bosch,Brembo,Dayco,Delphi,FAG,FILTRON,HEPU,INA,KNECHT,LEMFÖRDER,LuK,MAHLE,MANN-FILTER,PURFLUX,ProVia,SACHS,SWAG,TEXTAR,TRW,VDO,Valeo,Vitesco Technologies,WABCO,ZF Parts,febi"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
